--- a/data/google_news_dedup_audit_02_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_02_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,164 +445,164 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6862471699714661</v>
+        <v>0.7852948904037476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Air France selects DHL Supply Chain to deliver ground handling services at London Gatwick - Passenger Terminal Today</t>
+          <t>Royal Mail issues delivery disruption alert for 28 postcodes today — full list - The Mirror</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
-        <v>7</v>
-      </c>
       <c r="C3" t="n">
-        <v>0.7231398224830627</v>
+        <v>0.7674502730369568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DHL Supply Chain appointed by Air France - Freightweek</t>
+          <t>Royal Mail issues delivery disruption alert for 4 Merseyside postcodes today — full list - Liverpool Echo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9146757125854492</v>
+        <v>0.6804190874099731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon drone delivery sparking privacy concerns in Metro Detroit - FOX 2 Detroit</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Privacy concerns mount over Amazon's delivery drones in Michigan - FOX 2 Detroit</t>
+          <t>Royal Mail delivery alert as 28 postcodes face delays — full list - Daily Express</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8205010890960693</v>
+        <v>0.6862471699714661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FedEx's same-day delivery rollout is more about optionality than speed - MSN</t>
+          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FedEx unveils ‘SameDay Local’ faster delivery service - MSN</t>
+          <t>Air France selects DHL Supply Chain to deliver ground handling services at London Gatwick - Passenger Terminal Today</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6658856272697449</v>
+        <v>0.7231398224830627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FedEx's same-day delivery rollout is more about optionality than speed - MSN</t>
+          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FedEx joins Amazon, Walmart in race to get goods to Americans faster with new same-day delivery service - MSN</t>
+          <t>DHL Supply Chain appointed by Air France - Freightweek</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5183743238449097</v>
+        <v>0.5452268123626709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
+          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
+          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - GVA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n">
         <v>19</v>
       </c>
-      <c r="B8" t="n">
-        <v>25</v>
-      </c>
       <c r="C8" t="n">
-        <v>0.8917389512062073</v>
+        <v>0.5183743238449097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - GVA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7399972677230835</v>
+        <v>0.7620973587036133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
+          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -613,211 +613,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8117684125900269</v>
+        <v>0.8777137398719788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
+          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12-year-old Dutch boy planned terrorist attack on the Flemish Parliament - VRT</t>
+          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - France Info</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7341318130493164</v>
+        <v>0.9249871969223022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Un tout jeune adolescent condamné aux Pays-Bas pour avoir planifié un attentat contre le Parlement flamand - VRT</t>
+          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Un jeune condamné aux Pays-Bas pour avoir planifié un attentat visant le parlement flamand - MSN</t>
+          <t>Attentat déjoué contre Bank of America à Paris : où en est l'enquête ? - TF1 Info</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5506068468093872</v>
+        <v>0.7324134707450867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
+          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extra police patrols in Shooters Hill after woman in her 80s fatally stabbed - london-now.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>70</v>
-      </c>
-      <c r="B13" t="n">
-        <v>74</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8780280351638794</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Woman in her 80s stabbed to death outside home in Shooters Hill - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>78</v>
-      </c>
-      <c r="B14" t="n">
-        <v>80</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7393731474876404</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Man, 18, charged with murder after stabbing near Westminster Abbey - london-now.co.uk</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Police name Leeds teenager charged with stabbing young man to death in Westminster - My London</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>85</v>
-      </c>
-      <c r="B15" t="n">
-        <v>87</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.6833537817001343</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bank of America : quatre jeunes mis en examen et écroués après l’attentat déjoué à Paris, imputable à un groupuscule pro-iranien - Le Parisien</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>85</v>
-      </c>
-      <c r="B16" t="n">
-        <v>88</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.805501401424408</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America à Paris : où en est l'enquête ? - TF1 Info</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>85</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.7067276835441589</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>Tentative d’attentat à Paris contre Bank of America: la justice explore la piste pro-iranienne - RFI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>85</v>
-      </c>
-      <c r="B18" t="n">
-        <v>91</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.674129843711853</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : une information judiciaire ouverte pour association de malfaiteurs terroriste - Le Monde.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>85</v>
-      </c>
-      <c r="B19" t="n">
-        <v>92</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7054390907287598</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America à Paris : une information judiciaire ouverte pour association de malfaiteurs terroriste - Le Parisien</t>
         </is>
       </c>
     </row>
